--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488067_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488067_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4934</v>
+        <v>5.8679</v>
       </c>
       <c r="E2" t="n">
-        <v>2.0831</v>
+        <v>1.8399</v>
       </c>
       <c r="F2" t="n">
-        <v>3.4102</v>
+        <v>4.028</v>
       </c>
       <c r="G2" t="n">
         <v>5.4457</v>
@@ -610,13 +610,13 @@
         <v>2.1805</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1922</v>
+        <v>-0.8177</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6202</v>
+        <v>-0.8633999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5721000000000001</v>
+        <v>0.0457</v>
       </c>
       <c r="V2" t="n">
         <v>-0.9405</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. AMAYA QUINTERO</t>
+          <t>D. GARCIA GAZQUEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3434</v>
+        <v>4.1797</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1331</v>
+        <v>-0.2783</v>
       </c>
       <c r="F3" t="n">
-        <v>4.2103</v>
+        <v>4.458</v>
       </c>
       <c r="G3" t="n">
-        <v>3.1995</v>
+        <v>1.6045</v>
       </c>
       <c r="H3" t="n">
-        <v>3.192</v>
+        <v>-0.8002</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0075</v>
+        <v>2.4047</v>
       </c>
       <c r="J3" t="n">
-        <v>1.3992</v>
+        <v>-0.1356</v>
       </c>
       <c r="K3" t="n">
-        <v>1.9578</v>
+        <v>-2.1043</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5586</v>
+        <v>1.9687</v>
       </c>
       <c r="M3" t="n">
-        <v>1.8003</v>
+        <v>1.7401</v>
       </c>
       <c r="N3" t="n">
-        <v>1.2342</v>
+        <v>1.3041</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5661</v>
+        <v>0.436</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1893</v>
+        <v>0.9911</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1805</v>
+        <v>2.9733</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3619</v>
+        <v>-0.5636</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1324</v>
+        <v>-0.8413</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2295</v>
+        <v>0.2778</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.4074</v>
+        <v>2.1476</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.4074</v>
+        <v>2.6808</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. GARCIA GAZQUEZ</t>
+          <t>S. AMAYA QUINTERO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.9168</v>
+        <v>3.7446</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.8501</v>
+        <v>-0.3534</v>
       </c>
       <c r="F4" t="n">
-        <v>4.7669</v>
+        <v>4.098</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6045</v>
+        <v>3.1995</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.8002</v>
+        <v>3.192</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4047</v>
+        <v>0.0075</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1356</v>
+        <v>1.3992</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.1043</v>
+        <v>1.9578</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9687</v>
+        <v>-0.5586</v>
       </c>
       <c r="M4" t="n">
-        <v>1.7401</v>
+        <v>1.8003</v>
       </c>
       <c r="N4" t="n">
-        <v>1.3041</v>
+        <v>1.2342</v>
       </c>
       <c r="O4" t="n">
-        <v>0.436</v>
+        <v>0.5661</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9911</v>
+        <v>1.1893</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R4" t="n">
-        <v>2.9733</v>
+        <v>2.1805</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8264</v>
+        <v>-0.2368</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.4131</v>
+        <v>-0.354</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5866</v>
+        <v>0.1172</v>
       </c>
       <c r="V4" t="n">
-        <v>2.1476</v>
+        <v>-0.4074</v>
       </c>
       <c r="W4" t="n">
-        <v>2.6808</v>
+        <v>-0.4074</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5331</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.7014</v>
+        <v>3.1193</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8522</v>
+        <v>2.1579</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8491</v>
+        <v>0.9614</v>
       </c>
       <c r="G6" t="n">
         <v>3.0378</v>
@@ -922,13 +922,13 @@
         <v>1.3876</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8538</v>
+        <v>-0.4359</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2899</v>
+        <v>0.0157</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5639</v>
+        <v>-0.4516</v>
       </c>
       <c r="V6" t="n">
         <v>-0.8701</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9485</v>
+        <v>1.7686</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6714</v>
+        <v>0.6319</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2771</v>
+        <v>1.1367</v>
       </c>
       <c r="G7" t="n">
         <v>1.8403</v>
@@ -1000,13 +1000,13 @@
         <v>1.5858</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2001</v>
+        <v>-0.38</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0586</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1415</v>
+        <v>-0.2819</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2775</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2743</v>
+        <v>1.5861</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3149</v>
+        <v>0.6829</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9594</v>
+        <v>0.9032</v>
       </c>
       <c r="G8" t="n">
         <v>-0.2905</v>
@@ -1078,13 +1078,13 @@
         <v>1.5858</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5918</v>
+        <v>-0.2799</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8112</v>
+        <v>-0.4432</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2194</v>
+        <v>0.1632</v>
       </c>
       <c r="V8" t="n">
         <v>2.7512</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ CANTERO</t>
+          <t>M. VIGO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4244</v>
+        <v>1.3939</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2224</v>
+        <v>-3.825</v>
       </c>
       <c r="F9" t="n">
-        <v>2.6468</v>
+        <v>5.219</v>
       </c>
       <c r="G9" t="n">
-        <v>1.3494</v>
+        <v>-2.389</v>
       </c>
       <c r="H9" t="n">
-        <v>1.2004</v>
+        <v>-2.6855</v>
       </c>
       <c r="I9" t="n">
-        <v>0.149</v>
+        <v>0.2965</v>
       </c>
       <c r="J9" t="n">
-        <v>1.507</v>
+        <v>-3.5822</v>
       </c>
       <c r="K9" t="n">
-        <v>1.3865</v>
+        <v>-2.9108</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1205</v>
+        <v>-0.6713</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1576</v>
+        <v>1.1932</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1861</v>
+        <v>0.2253</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0285</v>
+        <v>0.9679</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.7929</v>
+        <v>3.568</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.1716</v>
+        <v>-0.1982</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3787</v>
+        <v>3.7662</v>
       </c>
       <c r="S9" t="n">
-        <v>1.0046</v>
+        <v>-0.6553</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5578</v>
+        <v>-0.9147999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>1.5624</v>
+        <v>0.2595</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.1367</v>
+        <v>0.8701</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.8701</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1367</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. VIGO RODRIGUEZ</t>
+          <t>J. RODRIGUEZ CANTERO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2824</v>
+        <v>-0.4646</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.4592</v>
+        <v>-2.4656</v>
       </c>
       <c r="F10" t="n">
-        <v>4.7416</v>
+        <v>2.001</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.389</v>
+        <v>1.3494</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.6855</v>
+        <v>1.2004</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2965</v>
+        <v>0.149</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.5822</v>
+        <v>1.507</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.9108</v>
+        <v>1.3865</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6713</v>
+        <v>0.1205</v>
       </c>
       <c r="M10" t="n">
-        <v>1.1932</v>
+        <v>-0.1576</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2253</v>
+        <v>-0.1861</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9679</v>
+        <v>0.0285</v>
       </c>
       <c r="P10" t="n">
-        <v>3.568</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1982</v>
+        <v>-3.1716</v>
       </c>
       <c r="R10" t="n">
-        <v>3.7662</v>
+        <v>2.3787</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.7667</v>
+        <v>0.1156</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.5489</v>
+        <v>-0.801</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2178</v>
+        <v>0.9166</v>
       </c>
       <c r="V10" t="n">
-        <v>0.8701</v>
+        <v>-1.1367</v>
       </c>
       <c r="W10" t="n">
-        <v>0.8701</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.1367</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7921</v>
+        <v>-1.8587</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.242</v>
+        <v>-2.1401</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4498</v>
+        <v>0.2814</v>
       </c>
       <c r="G11" t="n">
         <v>-0.9697</v>
@@ -1312,13 +1312,13 @@
         <v>2.3787</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4171</v>
+        <v>-0.4837</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8736</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4565</v>
+        <v>0.288</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6036</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.0713</v>
+        <v>-2.1917</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.2732</v>
+        <v>-1.6183</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.798</v>
+        <v>-0.5734</v>
       </c>
       <c r="G12" t="n">
         <v>-0.951</v>
@@ -1390,13 +1390,13 @@
         <v>1.3876</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3274</v>
+        <v>-0.4478</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0696</v>
+        <v>-0.4147</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2577</v>
+        <v>-0.0331</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,31 +1423,31 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>19.8452</v>
+        <v>20.4691</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.668200000000001</v>
+        <v>-2.0441</v>
       </c>
       <c r="F13" t="n">
-        <v>22.5132</v>
+        <v>22.5133</v>
       </c>
       <c r="G13" t="n">
         <v>15.201</v>
       </c>
       <c r="H13" t="n">
-        <v>9.739399999999998</v>
+        <v>9.7394</v>
       </c>
       <c r="I13" t="n">
-        <v>5.461400000000001</v>
+        <v>5.4614</v>
       </c>
       <c r="J13" t="n">
         <v>10.1103</v>
       </c>
       <c r="K13" t="n">
-        <v>7.564799999999999</v>
+        <v>7.564800000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>2.545500000000001</v>
+        <v>2.5455</v>
       </c>
       <c r="M13" t="n">
         <v>5.090700000000001</v>
@@ -1456,10 +1456,10 @@
         <v>2.1746</v>
       </c>
       <c r="O13" t="n">
-        <v>2.9161</v>
+        <v>2.916100000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>8.92</v>
+        <v>8.920000000000002</v>
       </c>
       <c r="Q13" t="n">
         <v>-12.8846</v>
@@ -1468,16 +1468,16 @@
         <v>21.8047</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.809</v>
+        <v>-4.1851</v>
       </c>
       <c r="T13" t="n">
-        <v>-6.1105</v>
+        <v>-5.486499999999999</v>
       </c>
       <c r="U13" t="n">
         <v>1.3014</v>
       </c>
       <c r="V13" t="n">
-        <v>0.5330999999999998</v>
+        <v>0.5330999999999996</v>
       </c>
       <c r="W13" t="n">
         <v>6.216600000000001</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. MARTIN GARCIA</t>
+          <t>A. VAZQUEZ GARCIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.5501</v>
+        <v>0.797</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4962</v>
+        <v>-0.9539</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0539</v>
+        <v>1.7509</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.2386</v>
+        <v>-0.4747</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.5173</v>
+        <v>-0.159</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.7214</v>
+        <v>-0.3157</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.4512</v>
+        <v>-0.1681</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.652</v>
+        <v>0.4306</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2009</v>
+        <v>-0.5988</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.7875</v>
+        <v>-0.3066</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.8652</v>
+        <v>-0.5896</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.9223</v>
+        <v>0.2831</v>
       </c>
       <c r="P14" t="n">
-        <v>0.1982</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q14" t="n">
         <v>-1.1893</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3876</v>
+        <v>0.7929</v>
       </c>
       <c r="S14" t="n">
-        <v>3.987</v>
+        <v>0.7277</v>
       </c>
       <c r="T14" t="n">
-        <v>2.5331</v>
+        <v>-0.1999</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4539</v>
+        <v>0.9276</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6036</v>
+        <v>0.9405</v>
       </c>
       <c r="W14" t="n">
         <v>0.6036</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. CRIADO SALVADOR</t>
+          <t>J. MARTIN GARCIA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5161</v>
+        <v>0.3619</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2279</v>
+        <v>-0.4393</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2882</v>
+        <v>0.8012</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2549</v>
+        <v>-2.2386</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.8854</v>
+        <v>-1.5173</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1403</v>
+        <v>-0.7214</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5629</v>
+        <v>-0.4512</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.3696</v>
+        <v>-0.652</v>
       </c>
       <c r="L15" t="n">
-        <v>1.9324</v>
+        <v>0.2009</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.308</v>
+        <v>-1.7875</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5158</v>
+        <v>-0.8652</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.7922</v>
+        <v>-0.9223</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.1805</v>
+        <v>0.1982</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.9645</v>
+        <v>-1.1893</v>
       </c>
       <c r="R15" t="n">
-        <v>1.784</v>
+        <v>1.3876</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5716</v>
+        <v>1.7987</v>
       </c>
       <c r="T15" t="n">
-        <v>2.0963</v>
+        <v>0.5976</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4752</v>
+        <v>1.2011</v>
       </c>
       <c r="V15" t="n">
-        <v>0.8701</v>
+        <v>0.6036</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5331</v>
+        <v>0.6036</v>
       </c>
       <c r="X15" t="n">
-        <v>0.337</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. VAZQUEZ GARCIA</t>
+          <t>J. PÁEZ ÁVILA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2809</v>
+        <v>0.3027</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.5651</v>
+        <v>0.3027</v>
       </c>
       <c r="F16" t="n">
-        <v>2.846</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4747</v>
+        <v>0.3027</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.159</v>
+        <v>0.3027</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3157</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1681</v>
+        <v>0.3027</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4306</v>
+        <v>0.3027</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5988</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3066</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5896</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2831</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.3964</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1893</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7929</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2115</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8112</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.0227</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9405</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.337</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. PÁEZ ÁVILA</t>
+          <t>J. CRIADO SALVADOR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3027</v>
+        <v>0.2982</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3027</v>
+        <v>-1.402</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1.7003</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3027</v>
+        <v>0.2549</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3027</v>
+        <v>-0.8854</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1.1403</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3027</v>
+        <v>1.5629</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3027</v>
+        <v>-0.3696</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.9324</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>-1.308</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-0.5158</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>-0.7922</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-2.1805</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-3.9645</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.784</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.3537</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>0.4664</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>0.8873</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.8701</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.5331</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.121</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1795</v>
+        <v>-0.4851</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0586</v>
+        <v>0.3909</v>
       </c>
       <c r="G18" t="n">
         <v>-0.3415</v>
@@ -1858,13 +1858,13 @@
         <v>1.3876</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8433</v>
+        <v>0.87</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6647</v>
+        <v>0.359</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1786</v>
+        <v>0.511</v>
       </c>
       <c r="V18" t="n">
         <v>3.1435</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>T. PARRA MENDIVIL</t>
+          <t>L. VIVAR MARTINEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0554</v>
+        <v>-1.3471</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.358</v>
+        <v>-3.8783</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3026</v>
+        <v>2.5311</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.7418</v>
+        <v>-1.5572</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3951</v>
+        <v>-1.9247</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.1369</v>
+        <v>0.3676</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.4933</v>
+        <v>-0.3811</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3834</v>
+        <v>-1.405</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.8767</v>
+        <v>1.0239</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2485</v>
+        <v>-1.1761</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0118</v>
+        <v>-0.5198</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2602</v>
+        <v>-0.6563</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.1982</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9911</v>
+        <v>-2.9733</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7929</v>
+        <v>1.784</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1512</v>
+        <v>0.0515</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8736</v>
+        <v>-0.5238</v>
       </c>
       <c r="U20" t="n">
-        <v>1.0248</v>
+        <v>0.5753</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.2666</v>
+        <v>1.3479</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2666</v>
+        <v>1.3479</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. VIVAR MARTINEZ</t>
+          <t>T. PARRA MENDIVIL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5611</v>
+        <v>-1.9404</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.5913</v>
+        <v>-3.1542</v>
       </c>
       <c r="F21" t="n">
-        <v>2.0303</v>
+        <v>1.2138</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.5572</v>
+        <v>-1.7418</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.9247</v>
+        <v>0.3951</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3676</v>
+        <v>-2.1369</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3811</v>
+        <v>-1.4933</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.405</v>
+        <v>0.3834</v>
       </c>
       <c r="L21" t="n">
-        <v>1.0239</v>
+        <v>-1.8767</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.1761</v>
+        <v>-0.2485</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5198</v>
+        <v>0.0118</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6563</v>
+        <v>-0.2602</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.1893</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.9733</v>
+        <v>-0.9911</v>
       </c>
       <c r="R21" t="n">
-        <v>1.784</v>
+        <v>0.7929</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1625</v>
+        <v>0.2661</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.2369</v>
+        <v>-0.6698</v>
       </c>
       <c r="U21" t="n">
-        <v>0.07439999999999999</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="V21" t="n">
-        <v>1.3479</v>
+        <v>-0.2666</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.3479</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3436</v>
+        <v>-2.7337</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.2086</v>
+        <v>-1.903</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.135</v>
+        <v>-0.8307</v>
       </c>
       <c r="G22" t="n">
         <v>-2.281</v>
@@ -2170,13 +2170,13 @@
         <v>0.7929</v>
       </c>
       <c r="S22" t="n">
-        <v>0.083</v>
+        <v>0.6929</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3082</v>
+        <v>-0.0026</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3912</v>
+        <v>0.6955</v>
       </c>
       <c r="V22" t="n">
         <v>-1.7403</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.8815</v>
+        <v>-3.2317</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.5168</v>
+        <v>-3.0074</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3647</v>
+        <v>-0.2243</v>
       </c>
       <c r="G23" t="n">
         <v>-3.2577</v>
@@ -2248,13 +2248,13 @@
         <v>1.5858</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6148</v>
+        <v>0.0349</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1232</v>
+        <v>-0.6138</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5083</v>
+        <v>0.6487000000000001</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6036</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.4295</v>
+        <v>-5.2097</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.3372</v>
+        <v>-4.7259</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0924</v>
+        <v>-0.4838</v>
       </c>
       <c r="G24" t="n">
         <v>-2.0539</v>
@@ -2326,13 +2326,13 @@
         <v>1.3876</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.66</v>
+        <v>0.5599</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6202</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0398</v>
+        <v>0.5688</v>
       </c>
       <c r="V24" t="n">
         <v>-0.9405</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.9122</v>
+        <v>-5.4991</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.5964</v>
+        <v>-2.6795</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.3159</v>
+        <v>-2.8196</v>
       </c>
       <c r="G25" t="n">
         <v>-1.6104</v>
@@ -2404,13 +2404,13 @@
         <v>0.9911</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.414</v>
+        <v>-0.0009</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.4351</v>
+        <v>-0.5183</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0212</v>
+        <v>0.5174</v>
       </c>
       <c r="V25" t="n">
         <v>-3.8879</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-19.8452</v>
+        <v>-18.4868</v>
       </c>
       <c r="E26" t="n">
-        <v>-22.5133</v>
+        <v>-22.5131</v>
       </c>
       <c r="F26" t="n">
-        <v>2.668</v>
+        <v>4.026199999999999</v>
       </c>
       <c r="G26" t="n">
         <v>-15.201</v>
@@ -2482,13 +2482,13 @@
         <v>12.8846</v>
       </c>
       <c r="S26" t="n">
-        <v>4.809100000000001</v>
+        <v>6.1673</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.301499999999999</v>
+        <v>-1.3014</v>
       </c>
       <c r="U26" t="n">
-        <v>6.1105</v>
+        <v>7.4687</v>
       </c>
       <c r="V26" t="n">
         <v>-0.5333000000000006</v>
